--- a/public/report_templates/caja/reportes/vchMovimientoMeta.xlsx
+++ b/public/report_templates/caja/reportes/vchMovimientoMeta.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredipymeApp\public\report_templates\caja\reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredypymeApp\public\report_templates\caja\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0ACBA8A-0928-4665-9E71-E2BC0CAAC62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B0E63B-6962-4A49-B760-22B834D11DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
   </bookViews>
@@ -80,10 +80,10 @@
     <t>(titulo)</t>
   </si>
   <si>
-    <t>GRUPO CREDIPYME</t>
-  </si>
-  <si>
     <t>(comentario)</t>
+  </si>
+  <si>
+    <t>CREDIPYME HUANCA SAC</t>
   </si>
 </sst>
 </file>
@@ -578,7 +578,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -657,7 +657,7 @@
     </row>
     <row r="12" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>

--- a/public/report_templates/caja/reportes/vchMovimientoMeta.xlsx
+++ b/public/report_templates/caja/reportes/vchMovimientoMeta.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredypymeApp\public\report_templates\caja\reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\CredypymeApp\public\report_templates\caja\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B0E63B-6962-4A49-B760-22B834D11DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FBF664-DF14-47FB-B04E-E31AC7635B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
   </bookViews>
   <sheets>
     <sheet name="vchMovimientoMeta" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
     <t>(comentario)</t>
   </si>
   <si>
-    <t>CREDIPYME HUANCA SAC</t>
+    <t>CREDIPYME HUANCA S.A.C</t>
   </si>
 </sst>
 </file>
@@ -222,15 +222,24 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="22" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -239,15 +248,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -577,18 +577,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
     </row>
     <row r="3" spans="1:5" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -596,42 +596,42 @@
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="8"/>
+      <c r="B7" s="12"/>
       <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="14"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
@@ -642,10 +642,10 @@
       <c r="C9" s="7"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="13"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
@@ -656,11 +656,11 @@
       <c r="C11" s="7"/>
     </row>
     <row r="12" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" spans="1:5" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
@@ -668,47 +668,42 @@
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
     </row>
     <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A16:C16"/>
@@ -718,6 +713,11 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.27559055118110237" right="0" top="0" bottom="0" header="0" footer="0"/>
